--- a/mlef_pipeline/results/DCR/HIGH_PDL1/RWD/results.xlsx
+++ b/mlef_pipeline/results/DCR/HIGH_PDL1/RWD/results.xlsx
@@ -473,17 +473,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.51 ± 0.06</t>
+          <t>0.48 ± 0.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.35 ± 0.10</t>
+          <t>0.28 ± 0.12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.81 ± 0.09</t>
+          <t>0.85 ± 0.06</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -503,17 +503,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="F3" t="n">
